--- a/Inventario_Acabados.xlsx
+++ b/Inventario_Acabados.xlsx
@@ -34,10 +34,10 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
@@ -48,7 +48,7 @@
       <color rgb="00C0392B"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -97,15 +102,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -113,22 +119,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -494,295 +490,486 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>INVENTARIO DE ACABADOS — CABERNET</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+          <t>INVENTARIO Y BITÁCORA DE ACABADOS — CABERNET</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1) EXISTENCIAS (presupuesto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Presentación</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Presupuesto (se tiene)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Requerido (take-off)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>En existencia</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Requerido (generador)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Diferencia</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Moret Arena</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Piso Moret Arena</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>caja 1.42 m² (2 pz)</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>117</v>
       </c>
-      <c r="D3" s="5" t="n">
-        <v>115</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>✔ suficiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Royal Walnut</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="D5" s="6" t="n">
+        <v>113</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Suficiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Piso Royal Walnut</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>caja 1.20 m² (5 pz)</t>
         </is>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C6" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D6" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>✔ suficiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Suficiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Urbania White</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>caja 1.36 m² (10 pz)</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E7" s="8" t="n">
         <v>-1</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>⚠ falta</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Malla Lyndhurst</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>pieza 0.30×0.60 m</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C8" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D8" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E8" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>✔ suficiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>EXTRAS / COMPLEMENTOS</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Suficiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2) BITÁCORA DE SALIDAS (registrar cada día cuánto piso sale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Presentación</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Cantidad que salió</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Frente / área</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Recibió</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Saldo en obra</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>3) EXTRAS / COMPLEMENTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Presentación / color</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Boquilla Cantera</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Boquilla Chocolate</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Boquilla Blanco</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Boquilla Plata</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Impermeabilizante para charola</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Pegavitro 20 kg</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Pegaporcelánico 20 kg</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr"/>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr"/>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="11" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr"/>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -798,295 +985,486 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>INVENTARIO DE ACABADOS — MERLOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+          <t>INVENTARIO Y BITÁCORA DE ACABADOS — MERLOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1) EXISTENCIAS (presupuesto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Presentación</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Presupuesto (se tiene)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Requerido (take-off)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>En existencia</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Requerido (generador)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Diferencia</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Moret Arena</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Piso Moret Arena</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>caja 1.42 m² (2 pz)</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="D3" s="5" t="n">
-        <v>98</v>
-      </c>
-      <c r="E3" s="6" t="n">
+      <c r="D5" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Suficiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Piso Royal Walnut</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>caja 1.20 m² (5 pz)</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Urbania White</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>caja 1.36 m² (10 pz)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Malla Lyndhurst</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>pieza 0.30×0.60 m</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>✔ suficiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Royal Walnut</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>caja 1.20 m² (5 pz)</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="E4" s="14" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>⚠ falta</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Urbania White</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>caja 1.36 m² (10 pz)</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>⚠ falta</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Malla Lyndhurst</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>pieza 0.30×0.60 m</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>✔ suficiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>EXTRAS / COMPLEMENTOS</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Suficiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2) BITÁCORA DE SALIDAS (registrar cada día cuánto piso sale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Presentación</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Cantidad que salió</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Frente / área</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Recibió</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Saldo en obra</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>3) EXTRAS / COMPLEMENTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Presentación / color</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Boquilla Cantera</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Boquilla Chocolate</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Boquilla Blanco</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Boquilla Plata</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Impermeabilizante para charola</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Pegavitro 20 kg</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Pegaporcelánico 20 kg</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr"/>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr"/>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="11" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr"/>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1102,295 +1480,486 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>INVENTARIO DE ACABADOS — CHARDONNAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+          <t>INVENTARIO Y BITÁCORA DE ACABADOS — CHARDONNAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1) EXISTENCIAS (presupuesto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Presentación</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Presupuesto (se tiene)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Requerido (take-off)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>En existencia</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Requerido (generador)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Diferencia</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Moret Arena</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Piso Moret Arena</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>caja 1.42 m² (2 pz)</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>127</v>
       </c>
-      <c r="D3" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>⚠ falta</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Royal Walnut</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="D5" s="6" t="n">
+        <v>128</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Piso Royal Walnut</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>caja 1.20 m² (5 pz)</t>
         </is>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C6" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D6" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E6" s="8" t="n">
         <v>-1</v>
       </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>⚠ falta</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Urbania White</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>caja 1.36 m² (10 pz)</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E7" s="8" t="n">
         <v>-1</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>⚠ falta</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Malla Lyndhurst</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>pieza 0.30×0.60 m</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C8" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D8" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E8" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>✔ suficiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>EXTRAS / COMPLEMENTOS</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Suficiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2) BITÁCORA DE SALIDAS (registrar cada día cuánto piso sale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Presentación</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Cantidad que salió</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Frente / área</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Recibió</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Saldo en obra</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>3) EXTRAS / COMPLEMENTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Presentación / color</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Boquilla Cantera</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Boquilla Chocolate</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Boquilla Blanco</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Boquilla Plata</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Impermeabilizante para charola</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Pegavitro 20 kg</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Pegaporcelánico 20 kg</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr"/>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr"/>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="11" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr"/>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Inventario_Acabados.xlsx
+++ b/Inventario_Acabados.xlsx
@@ -1552,10 +1552,10 @@
         <v>127</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>

--- a/Inventario_Acabados.xlsx
+++ b/Inventario_Acabados.xlsx
@@ -562,10 +562,10 @@
         <v>117</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -1057,10 +1057,10 @@
         <v>98</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -1552,14 +1552,14 @@
         <v>127</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>129</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>-2</v>
+        <v>127</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Falta</t>
+          <t>Suficiente</t>
         </is>
       </c>
     </row>

--- a/Inventario_Acabados.xlsx
+++ b/Inventario_Acabados.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cabernet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Merlot" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Chardonnay" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Control de Lotes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cabernet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Merlot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Chardonnay" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,11 +34,15 @@
       <sz val="14"/>
     </font>
     <font>
-      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -62,12 +67,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
+        <fgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -76,7 +81,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -98,32 +103,73 @@
         <color rgb="00BBBBBB"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BBBBBB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -490,58 +536,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>INVENTARIO Y BITÁCORA DE ACABADOS — CABERNET</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>1) EXISTENCIAS (presupuesto)</t>
+          <t>CONTROL DE LOTES — SUMINISTRADO vs REQUERIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Cada lote se liga a su modelo. 'Requerido' sale del generador del modelo; 'Suministrado' arranca con el presupuesto y se puede editar conforme llega material.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Lote</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Manzana</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Presentación</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>En existencia</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Requerido (generador)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Requerido (cajas)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Suministrado (cajas)</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Diferencia</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
@@ -550,143 +614,198 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>L34</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Cabernet</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
           <t>Piso Moret Arena</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>caja 1.42 m² (2 pz)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="F5" s="7" t="n">
+        <v>112</v>
+      </c>
+      <c r="G5" s="7" t="n">
         <v>117</v>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>112</v>
-      </c>
-      <c r="E5" s="7" t="n">
+      <c r="H5" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Suficiente</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="9" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Piso Royal Walnut</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>caja 1.20 m² (5 pz)</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="G6" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="H6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>Suficiente</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="9" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Urbania White</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>caja 1.36 m² (10 pz)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="F7" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="D7" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" s="8" t="n">
+      <c r="H7" s="10" t="n">
         <v>-1</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>Falta</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Malla Lyndhurst</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>pieza 0.30×0.60 m</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="F8" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="E8" s="7" t="n">
+      <c r="H8" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>Suficiente</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2) BITÁCORA DE SALIDAS (registrar cada día cuánto piso sale)</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Merlot</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Piso Moret Arena</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>caja 1.42 m² (2 pz)</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Suficiente</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Cantidad que salió</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Frente / área</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Recibió</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Saldo en obra</t>
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Piso Royal Walnut</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>caja 1.20 m² (5 pz)</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Falta</t>
         </is>
       </c>
     </row>
@@ -694,286 +813,201 @@
       <c r="A12" s="9" t="n"/>
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Urbania White</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>caja 1.36 m² (10 pz)</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Malla Lyndhurst</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>pieza 0.30×0.60 m</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Suficiente</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Merlot</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Piso Moret Arena</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>caja 1.42 m² (2 pz)</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Suficiente</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n"/>
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Piso Royal Walnut</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>caja 1.20 m² (5 pz)</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Urbania White</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>caja 1.36 m² (10 pz)</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="9" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="n"/>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="n"/>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="n"/>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="n"/>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="n"/>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="n"/>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="9" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>3) EXTRAS / COMPLEMENTOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>Presentación / color</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>Observaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>Boquilla Cantera</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>Boquilla Chocolate</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="11" t="n"/>
-      <c r="F38" s="11" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>Boquilla Blanco</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="11" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>Boquilla Plata</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="11" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>Impermeabilizante para charola</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="11" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr"/>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="11" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr"/>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="11" t="n"/>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="n"/>
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Malla Lyndhurst</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>pieza 0.30×0.60 m</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Suficiente</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="11">
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="A10:A13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -999,12 +1033,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>INVENTARIO Y BITÁCORA DE ACABADOS — MERLOT</t>
+          <t>INVENTARIO Y BITÁCORA DE ACABADOS — CABERNET</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>1) EXISTENCIAS (presupuesto)</t>
         </is>
@@ -1043,111 +1077,111 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Piso Moret Arena</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>caja 1.42 m² (2 pz)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
-        <v>98</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>95</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="C5" s="7" t="n">
+        <v>117</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>112</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Suficiente</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Piso Royal Walnut</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>caja 1.20 m² (5 pz)</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>39</v>
+      <c r="C6" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>41</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Suficiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Urbania White</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>caja 1.36 m² (10 pz)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Falta</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Urbania White</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>caja 1.36 m² (10 pz)</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Falta</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Malla Lyndhurst</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>pieza 0.30×0.60 m</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="D8" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="E8" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Suficiente</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>2) BITÁCORA DE SALIDAS (registrar cada día cuánto piso sale)</t>
         </is>
@@ -1186,285 +1220,285 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n"/>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n"/>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="9" t="n"/>
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n"/>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n"/>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n"/>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="n"/>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9" t="n"/>
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="n"/>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="n"/>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="9" t="n"/>
+      <c r="A32" s="13" t="n"/>
+      <c r="B32" s="13" t="n"/>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="13" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>3) EXTRAS / COMPLEMENTOS</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>Presentación / color</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D36" s="14" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Boquilla Cantera</t>
         </is>
       </c>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="15" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Boquilla Chocolate</t>
         </is>
       </c>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="11" t="n"/>
-      <c r="F38" s="11" t="n"/>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="15" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Boquilla Blanco</t>
         </is>
       </c>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="11" t="n"/>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Boquilla Plata</t>
         </is>
       </c>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="11" t="n"/>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="15" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>Impermeabilizante para charola</t>
         </is>
       </c>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="11" t="n"/>
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="15" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr"/>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="11" t="n"/>
+      <c r="A42" s="15" t="inlineStr"/>
+      <c r="B42" s="15" t="n"/>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="15" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="15" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr"/>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="11" t="n"/>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="n"/>
+      <c r="A43" s="15" t="inlineStr"/>
+      <c r="B43" s="15" t="n"/>
+      <c r="C43" s="15" t="n"/>
+      <c r="D43" s="15" t="n"/>
+      <c r="E43" s="15" t="n"/>
+      <c r="F43" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1494,12 +1528,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>INVENTARIO Y BITÁCORA DE ACABADOS — CHARDONNAY</t>
+          <t>INVENTARIO Y BITÁCORA DE ACABADOS — MERLOT</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>1) EXISTENCIAS (presupuesto)</t>
         </is>
@@ -1538,111 +1572,111 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Piso Moret Arena</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>caja 1.42 m² (2 pz)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
-        <v>127</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>127</v>
-      </c>
-      <c r="E5" s="7" t="n">
+      <c r="C5" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Suficiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Piso Royal Walnut</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>caja 1.20 m² (5 pz)</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Urbania White</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>caja 1.36 m² (10 pz)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Malla Lyndhurst</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>pieza 0.30×0.60 m</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="E8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Suficiente</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Piso Royal Walnut</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>caja 1.20 m² (5 pz)</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Falta</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Urbania White</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>caja 1.36 m² (10 pz)</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Falta</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Malla Lyndhurst</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>pieza 0.30×0.60 m</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Suficiente</t>
-        </is>
-      </c>
-    </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>2) BITÁCORA DE SALIDAS (registrar cada día cuánto piso sale)</t>
         </is>
@@ -1681,285 +1715,780 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n"/>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n"/>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="9" t="n"/>
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n"/>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n"/>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n"/>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="n"/>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9" t="n"/>
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="n"/>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="n"/>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="9" t="n"/>
+      <c r="A32" s="13" t="n"/>
+      <c r="B32" s="13" t="n"/>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="13" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>3) EXTRAS / COMPLEMENTOS</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>Presentación / color</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D36" s="14" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Boquilla Cantera</t>
         </is>
       </c>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="15" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Boquilla Chocolate</t>
         </is>
       </c>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="11" t="n"/>
-      <c r="F38" s="11" t="n"/>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="15" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Boquilla Blanco</t>
         </is>
       </c>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="11" t="n"/>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Boquilla Plata</t>
         </is>
       </c>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="11" t="n"/>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="15" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>Impermeabilizante para charola</t>
         </is>
       </c>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="11" t="n"/>
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="15" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr"/>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="11" t="n"/>
+      <c r="A42" s="15" t="inlineStr"/>
+      <c r="B42" s="15" t="n"/>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="15" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="15" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr"/>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="11" t="n"/>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="n"/>
+      <c r="A43" s="15" t="inlineStr"/>
+      <c r="B43" s="15" t="n"/>
+      <c r="C43" s="15" t="n"/>
+      <c r="D43" s="15" t="n"/>
+      <c r="E43" s="15" t="n"/>
+      <c r="F43" s="15" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>INVENTARIO Y BITÁCORA DE ACABADOS — CHARDONNAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>1) EXISTENCIAS (presupuesto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Presentación</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>En existencia</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Requerido (generador)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Diferencia</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Piso Moret Arena</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>caja 1.42 m² (2 pz)</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>127</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>127</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Suficiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Piso Royal Walnut</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>caja 1.20 m² (5 pz)</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Urbania White</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>caja 1.36 m² (10 pz)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Malla Lyndhurst</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>pieza 0.30×0.60 m</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Suficiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>2) BITÁCORA DE SALIDAS (registrar cada día cuánto piso sale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Cantidad que salió</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Frente / área</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Recibió</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Saldo en obra</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n"/>
+      <c r="B32" s="13" t="n"/>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="13" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>3) EXTRAS / COMPLEMENTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Presentación / color</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>Boquilla Cantera</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="15" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>Boquilla Chocolate</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="15" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Boquilla Blanco</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>Boquilla Plata</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="15" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>Impermeabilizante para charola</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="15" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr"/>
+      <c r="B42" s="15" t="n"/>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="15" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="15" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr"/>
+      <c r="B43" s="15" t="n"/>
+      <c r="C43" s="15" t="n"/>
+      <c r="D43" s="15" t="n"/>
+      <c r="E43" s="15" t="n"/>
+      <c r="F43" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
